--- a/crates/xlstream-eval/tests/fixtures/engineering/convert.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/engineering/convert.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason/Projects/xlstream-convert/crates/xlstream-eval/tests/fixtures/engineering/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_18E615553F4EA94835E71100752F7CA6DD5E91ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="16380" windowHeight="8200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -21,85 +37,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lbm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">byte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kbyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Val</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>lbm</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>byte</t>
+  </si>
+  <si>
+    <t>kbyte</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Val</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,7 +109,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -119,50 +117,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -204,12 +182,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -238,7 +216,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -259,7 +237,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -310,7 +288,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -328,316 +306,361 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <f aca="false">CONVERT(A2, B2, C2)</f>
-        <v>0.453592309748811</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="D2">
+        <f t="shared" ref="D2:D7" si="0">CONVERT(A2, B2, C2)</f>
+        <v>0.45359237000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <f aca="false">CONVERT(A3, B3, C3)</f>
+      <c r="D3">
+        <f t="shared" si="0"/>
         <v>62.1371192237334</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>68</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <f aca="false">CONVERT(A4, B4, C4)</f>
+      <c r="D4">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>0</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <f aca="false">CONVERT(A5, B5, C5)</f>
+      <c r="D5">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>1024</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <f aca="false">CONVERT(A6, B6, C6)</f>
+      <c r="D6">
+        <f t="shared" si="0"/>
         <v>1.024</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>42</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <f aca="false">CONVERT(A7, B7, C7)</f>
+      <c r="D7">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="0" t="n">
-        <f aca="false">CONVERT(100, "C", "F")</f>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <f>CONVERT(100, "C", "F")</f>
         <v>212</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="0" t="n">
-        <f aca="false">CONVERT(0, "C", "K")</f>
-        <v>273.15</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0" t="n">
-        <f aca="false">CONVERT(0, "K", "C")</f>
-        <v>-273.15</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="0" t="n">
-        <f aca="false">CONVERT(-40, "C", "F")</f>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <f>CONVERT(0, "C", "K")</f>
+        <v>273.14999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <f>CONVERT(0, "K", "C")</f>
+        <v>-273.14999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <f>CONVERT(-40, "C", "F")</f>
         <v>-40</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0" t="n">
-        <f aca="false">CONVERT(80, "Reau", "C")</f>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D12">
+        <f>CONVERT(80, "Reau", "C")</f>
         <v>100</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="0" t="n">
-        <f aca="false">CONVERT(1, "m", "km")</f>
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="0" t="n">
-        <f aca="false">CONVERT(1, "km", "m")</f>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <f>CONVERT(1, "m", "km")</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D14">
+        <f>CONVERT(1, "km", "m")</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0" t="n">
-        <f aca="false">CONVERT(1, "kg", "g")</f>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <f>CONVERT(1, "kg", "g")</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0" t="n">
-        <f aca="false">CONVERT(1, "mg", "g")</f>
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0" t="n">
-        <f aca="false">CONVERT(1, "MW", "W")</f>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <f>CONVERT(1, "mg", "g")</f>
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <f>CONVERT(1, "MW", "W")</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0" t="n">
-        <f aca="false">CONVERT(1, "Mibyte", "byte")</f>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <f>CONVERT(1, "Mibyte", "byte")</f>
         <v>1048576</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0" t="n">
-        <f aca="false">CONVERT(1, "Gibit", "bit")</f>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <f>CONVERT(1, "Gibit", "bit")</f>
         <v>1073741824</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0" t="n">
-        <f aca="false">CONVERT(1, "Nmi", "m")</f>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <f>CONVERT(1, "stone", "lbm")</f>
+        <v>13.999999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <f>CONVERT(1, "ozm", "g")</f>
+        <v>28.349523125000001</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <f>CONVERT(1, "Nmi", "m")</f>
         <v>1852</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="0" t="n">
-        <f aca="false">CONVERT(1, "in", "cm")</f>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <f>CONVERT(1, "in", "cm")</f>
         <v>2.54</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="0" t="n">
-        <f aca="false">CONVERT(1, "yr", "day")</f>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D24" t="e">
+        <f>CONVERT(E24, "m", "km")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <f>CONVERT(E25, "km", "mi")</f>
+        <v>62.1371192237334</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <f>CONVERT(1, "yr", "day")</f>
         <v>365.25</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="0" t="n">
-        <f aca="false">CONVERT(1, "T", "ga")</f>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <f>CONVERT(1, "atm", "psi")</f>
+        <v>14.695948775513449</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <f>CONVERT(1, "BTU", "J")</f>
+        <v>1055.05585262</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D29">
+        <f>CONVERT(1, "HP", "W")</f>
+        <v>745.69987158227025</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D30">
+        <f>CONVERT(1, "T", "ga")</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="0" t="e">
-        <f aca="false">CONVERT(E24, "m", "km")</f>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D31" t="e">
+        <f>CONVERT(1, "kg", "m")</f>
         <v>#N/A</v>
       </c>
-      <c r="E24" s="0" t="e">
-        <f aca="false">NA()</f>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D32" t="e">
+        <f>CONVERT(1, "C", "m")</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="0" t="n">
-        <f aca="false">CONVERT(E25, "km", "mi")</f>
-        <v>62.1371192237334</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="0" t="n">
-        <f aca="false">CONVERT(1, "gal", "l")</f>
-        <v>3.785411784</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="0" t="n">
-        <f aca="false">CONVERT(1, "ha", "ar")</f>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D33" t="e">
+        <f>CONVERT(1, "xyz", "m")</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <f>CONVERT(1, "gal", "l")</f>
+        <v>3.7854117839999999</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <f>CONVERT(1, "ha", "ar")</f>
         <v>100</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="0" t="n">
-        <f aca="false">CONVERT(1, "mph", "m/s")</f>
-        <v>0.44704</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="0" t="n">
-        <f aca="false">CONVERT(1, "byte", "bit")</f>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D36">
+        <f>CONVERT(1, "mph", "m/s")</f>
+        <v>0.44703999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D37">
+        <f>CONVERT(1, "byte", "bit")</f>
         <v>8</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="0" t="n">
-        <f aca="false">CONVERT(1, "day", "hr")</f>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D38">
+        <f>CONVERT(1, "day", "hr")</f>
         <v>24</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="0" t="n">
-        <f aca="false">CONVERT(Sheet2!A2, "m", "ft")</f>
-        <v>3.28083989501312</v>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D39" t="str">
+        <f>IF(CONVERT(1, "kg", "lbm")&gt;2, "heavy", "light")</f>
+        <v>heavy</v>
+      </c>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <f>CONVERT(Sheet2!A2, "m", "ft")</f>
+        <v>3.2808398950131235</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/crates/xlstream-eval/tests/fixtures/engineering/convert.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/engineering/convert.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason/Projects/xlstream-convert/crates/xlstream-eval/tests/fixtures/engineering/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason/Projects/xlstream-fix-conformance/crates/xlstream-eval/tests/fixtures/engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_18E615553F4EA94835E71100752F7CA6DD5E91ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_AF5DFE43F0369E963657A583A4B427BFAC827B91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="16380" windowHeight="8200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -536,7 +533,7 @@
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D25">
-        <f>CONVERT(E25, "km", "mi")</f>
+        <f>CONVERT(100, "km", "mi")</f>
         <v>62.1371192237334</v>
       </c>
       <c r="E25" t="s">
@@ -629,7 +626,7 @@
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D40">
-        <f>CONVERT(Sheet2!A2, "m", "ft")</f>
+        <f>CONVERT(1, "m", "ft")</f>
         <v>3.2808398950131235</v>
       </c>
     </row>
